--- a/data/manual/全台ACG活動.xlsx
+++ b/data/manual/全台ACG活動.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q118"/>
+  <dimension ref="A1:Q128"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="14.33203125" customWidth="1" style="9" min="2" max="2"/>
@@ -8385,6 +8385,746 @@
         </is>
       </c>
       <c r="Q118" s="17" t="n">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="inlineStr">
+        <is>
+          <t>https://nte.iwplay.com.tw/news/CmsnewsImg/2000213/build/2026070814383629066473.png</t>
+        </is>
+      </c>
+      <c r="B119" s="0" t="inlineStr">
+        <is>
+          <t>物販/Goods</t>
+        </is>
+      </c>
+      <c r="C119" s="0" t="inlineStr">
+        <is>
+          <t>主題餐廳/Theme Cafe</t>
+        </is>
+      </c>
+      <c r="D119" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E119" s="0" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F119" s="19" t="n">
+        <v>46220</v>
+      </c>
+      <c r="G119" s="19" t="n">
+        <v>46245</v>
+      </c>
+      <c r="H119" s="0" t="inlineStr">
+        <is>
+          <t>異環</t>
+        </is>
+      </c>
+      <c r="I119" s="0" t="inlineStr">
+        <is>
+          <t>異環 x FanFans Café｜期間限定主題餐廳</t>
+        </is>
+      </c>
+      <c r="J119" s="0" t="inlineStr">
+        <is>
+          <t>台北西門店（台北市萬華區昆明街92之1號5樓）</t>
+        </is>
+      </c>
+      <c r="K119" s="0" t="inlineStr">
+        <is>
+          <t>FanFans Café</t>
+        </is>
+      </c>
+      <c r="L119" s="0" t="inlineStr">
+        <is>
+          <t>Hotta Studio（a Perfect World company）</t>
+        </is>
+      </c>
+      <c r="M119" s="0" t="inlineStr">
+        <is>
+          <t>https://nte.iwplay.com.tw/news/view/20260708/f261ed96.html</t>
+        </is>
+      </c>
+      <c r="N119" s="0" t="inlineStr">
+        <is>
+          <t>資料與KV來源：《異環》官方新聞頁(nte.iwplay.com.tw)，KV圖片已下載並肉眼確認含活動名稱/雙店名/日期(7/17~8/11)/版權標示(© Hotta Studio, a Perfect World company)。原Slack連結為IG，已依官方新聞頁替換。</t>
+        </is>
+      </c>
+      <c r="O119" s="0" t="inlineStr">
+        <is>
+          <t>異環</t>
+        </is>
+      </c>
+      <c r="P119" s="0" t="inlineStr">
+        <is>
+          <t>Hotta Studio</t>
+        </is>
+      </c>
+      <c r="Q119" s="17" t="n">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="inlineStr">
+        <is>
+          <t>https://nte.iwplay.com.tw/news/CmsnewsImg/2000213/build/2026070814383629066473.png</t>
+        </is>
+      </c>
+      <c r="B120" s="0" t="inlineStr">
+        <is>
+          <t>物販/Goods</t>
+        </is>
+      </c>
+      <c r="C120" s="0" t="inlineStr">
+        <is>
+          <t>主題餐廳/Theme Cafe</t>
+        </is>
+      </c>
+      <c r="D120" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E120" s="0" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F120" s="19" t="n">
+        <v>46220</v>
+      </c>
+      <c r="G120" s="19" t="n">
+        <v>46245</v>
+      </c>
+      <c r="H120" s="0" t="inlineStr">
+        <is>
+          <t>異環</t>
+        </is>
+      </c>
+      <c r="I120" s="0" t="inlineStr">
+        <is>
+          <t>異環 x FanFans Café｜期間限定主題餐廳</t>
+        </is>
+      </c>
+      <c r="J120" s="0" t="inlineStr">
+        <is>
+          <t>高雄愛河店（高雄市前金區大同二路23號1樓）</t>
+        </is>
+      </c>
+      <c r="K120" s="0" t="inlineStr">
+        <is>
+          <t>FanFans Café</t>
+        </is>
+      </c>
+      <c r="L120" s="0" t="inlineStr">
+        <is>
+          <t>Hotta Studio（a Perfect World company）</t>
+        </is>
+      </c>
+      <c r="M120" s="0" t="inlineStr">
+        <is>
+          <t>https://nte.iwplay.com.tw/news/view/20260708/f261ed96.html</t>
+        </is>
+      </c>
+      <c r="N120" s="0" t="inlineStr">
+        <is>
+          <t>資料與KV來源：《異環》官方新聞頁(nte.iwplay.com.tw)，KV圖片已下載並肉眼確認含活動名稱/雙店名/日期(7/17~8/11)/版權標示(© Hotta Studio, a Perfect World company)。原Slack連結為IG，已依官方新聞頁替換。</t>
+        </is>
+      </c>
+      <c r="O120" s="0" t="inlineStr">
+        <is>
+          <t>異環</t>
+        </is>
+      </c>
+      <c r="P120" s="0" t="inlineStr">
+        <is>
+          <t>Hotta Studio</t>
+        </is>
+      </c>
+      <c r="Q120" s="17" t="n">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="0" t="inlineStr">
+        <is>
+          <t>物販/Goods</t>
+        </is>
+      </c>
+      <c r="C121" s="0" t="inlineStr">
+        <is>
+          <t>體驗活動/Experience Activity</t>
+        </is>
+      </c>
+      <c r="D121" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E121" s="0" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F121" s="19" t="n">
+        <v>46256</v>
+      </c>
+      <c r="G121" s="19" t="n">
+        <v>46256</v>
+      </c>
+      <c r="H121" s="0" t="inlineStr">
+        <is>
+          <t>伊藤潤二</t>
+        </is>
+      </c>
+      <c r="I121" s="0" t="inlineStr">
+        <is>
+          <t>伊藤潤二狂熱城市夜行路跑</t>
+        </is>
+      </c>
+      <c r="J121" s="0" t="inlineStr">
+        <is>
+          <t>新北微風運河（確切門牌新聞未載明，需人工確認）</t>
+        </is>
+      </c>
+      <c r="K121" s="0" t="inlineStr">
+        <is>
+          <t>木棉花</t>
+        </is>
+      </c>
+      <c r="L121" s="0" t="inlineStr">
+        <is>
+          <t>木棉花</t>
+        </is>
+      </c>
+      <c r="M121" s="0" t="inlineStr">
+        <is>
+          <t>https://www.bryte-fun.com</t>
+        </is>
+      </c>
+      <c r="N121" s="0" t="inlineStr">
+        <is>
+          <t>資料來源：木棉花Muse官方新聞稿(ccpa.org.tw/ccpa/data.php?id=661)、中央社CNA(howlife.cna.com.tw/life/20260610s003.aspx)、巴哈姆特GNN(sn=306474)等多家新聞確認日期。報名連結修正為官方網域bryte-fun.com（原Slack訊息網域bryte.event有誤，查無該網域）。活動類別「體驗活動」為AI判斷（沉浸式夜跑非典型四類之一，請確認是否合適）。</t>
+        </is>
+      </c>
+      <c r="O121" s="0" t="inlineStr">
+        <is>
+          <t>伊藤潤二</t>
+        </is>
+      </c>
+      <c r="P121" s="0" t="inlineStr">
+        <is>
+          <t>木棉花</t>
+        </is>
+      </c>
+      <c r="Q121" s="17" t="n">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="0" t="inlineStr">
+        <is>
+          <t>物販/Goods</t>
+        </is>
+      </c>
+      <c r="C122" s="0" t="inlineStr">
+        <is>
+          <t>體驗活動/Experience Activity</t>
+        </is>
+      </c>
+      <c r="D122" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E122" s="0" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F122" s="19" t="n">
+        <v>46263</v>
+      </c>
+      <c r="G122" s="19" t="n">
+        <v>46263</v>
+      </c>
+      <c r="H122" s="0" t="inlineStr">
+        <is>
+          <t>伊藤潤二</t>
+        </is>
+      </c>
+      <c r="I122" s="0" t="inlineStr">
+        <is>
+          <t>伊藤潤二狂熱城市夜行路跑</t>
+        </is>
+      </c>
+      <c r="J122" s="0" t="inlineStr">
+        <is>
+          <t>台中東海大學（台中市西屯區台灣大道四段1727號）</t>
+        </is>
+      </c>
+      <c r="K122" s="0" t="inlineStr">
+        <is>
+          <t>木棉花</t>
+        </is>
+      </c>
+      <c r="L122" s="0" t="inlineStr">
+        <is>
+          <t>木棉花</t>
+        </is>
+      </c>
+      <c r="M122" s="0" t="inlineStr">
+        <is>
+          <t>https://www.bryte-fun.com</t>
+        </is>
+      </c>
+      <c r="N122" s="0" t="inlineStr">
+        <is>
+          <t>資料來源：木棉花Muse官方新聞稿(ccpa.org.tw/ccpa/data.php?id=661)、中央社CNA(howlife.cna.com.tw/life/20260610s003.aspx)、巴哈姆特GNN(sn=306474)等多家新聞確認日期。報名連結修正為官方網域bryte-fun.com（原Slack訊息網域bryte.event有誤，查無該網域）。活動類別「體驗活動」為AI判斷（沉浸式夜跑非典型四類之一，請確認是否合適）。</t>
+        </is>
+      </c>
+      <c r="O122" s="0" t="inlineStr">
+        <is>
+          <t>伊藤潤二</t>
+        </is>
+      </c>
+      <c r="P122" s="0" t="inlineStr">
+        <is>
+          <t>木棉花</t>
+        </is>
+      </c>
+      <c r="Q122" s="17" t="n">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="0" t="inlineStr">
+        <is>
+          <t>物販/Goods</t>
+        </is>
+      </c>
+      <c r="C123" s="0" t="inlineStr">
+        <is>
+          <t>體驗活動/Experience Activity</t>
+        </is>
+      </c>
+      <c r="D123" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E123" s="0" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F123" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="G123" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="H123" s="0" t="inlineStr">
+        <is>
+          <t>CookieRun</t>
+        </is>
+      </c>
+      <c r="I123" s="0" t="inlineStr">
+        <is>
+          <t>2026來嘉BIKE訪．騎聚好歡樂 x CookieRun薑餅人（7/18加開場）</t>
+        </is>
+      </c>
+      <c r="J123" s="0" t="inlineStr">
+        <is>
+          <t>蘭潭音樂噴泉（嘉義市東區紅毛埤187號）／檢錄地點：嘉義大學蘭潭校區－瑞穗館前（嘉義市鹿寮里學府路300號）</t>
+        </is>
+      </c>
+      <c r="K123" s="0" t="inlineStr">
+        <is>
+          <t>嘉義市政府</t>
+        </is>
+      </c>
+      <c r="L123" s="0" t="inlineStr">
+        <is>
+          <t>CookieRun（Devsisters，需人工確認正式台灣授權單位名稱）</t>
+        </is>
+      </c>
+      <c r="M123" s="0" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DazKEN1jqZZ</t>
+        </is>
+      </c>
+      <c r="N123" s="0" t="inlineStr">
+        <is>
+          <t>原Slack訊息日期(7/18)與嘉義市政府官網(travel.chiayi.gov.tw)所載首場日期(6/13)不同；經查CookieRun Taiwan官方IG(@cookieruntw)於2026/07/15發布之貼文確認7/18(六)為加開場次，地點與6/13首場一致，故採用7/18。連結為官方IP帳號直發貼文（非二手轉貼），依使用者指示使用IG來源。活動類別「體驗活動」為AI判斷。</t>
+        </is>
+      </c>
+      <c r="O123" s="0" t="inlineStr">
+        <is>
+          <t>CookieRun</t>
+        </is>
+      </c>
+      <c r="P123" s="0" t="inlineStr">
+        <is>
+          <t>需人工確認</t>
+        </is>
+      </c>
+      <c r="Q123" s="17" t="n">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="0" t="inlineStr">
+        <is>
+          <t>物販/Goods</t>
+        </is>
+      </c>
+      <c r="C124" s="0" t="inlineStr">
+        <is>
+          <t>快閃店/Pop-up Store</t>
+        </is>
+      </c>
+      <c r="D124" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E124" s="0" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F124" s="19" t="n">
+        <v>46216</v>
+      </c>
+      <c r="G124" s="19" t="n">
+        <v>46236</v>
+      </c>
+      <c r="H124" s="0" t="inlineStr">
+        <is>
+          <t>角落小夥伴</t>
+        </is>
+      </c>
+      <c r="I124" s="0" t="inlineStr">
+        <is>
+          <t>角落小夥伴水族館第2彈</t>
+        </is>
+      </c>
+      <c r="J124" s="0" t="inlineStr">
+        <is>
+          <t>三創生活園區1F（台北市中正區市民大道三段2號）</t>
+        </is>
+      </c>
+      <c r="K124" s="0" t="inlineStr">
+        <is>
+          <t>勝明文具</t>
+        </is>
+      </c>
+      <c r="L124" s="0" t="inlineStr">
+        <is>
+          <t>SAN-X</t>
+        </is>
+      </c>
+      <c r="M124" s="0" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sanminsupergift/posts/1463007639194294/</t>
+        </is>
+      </c>
+      <c r="N124" s="0" t="inlineStr">
+        <is>
+          <t>資料來源：勝明文具(SAN-X台灣代理)官方Facebook專頁，貼文日期2026/07/13，內容寫「即日起～8/2」；開始日期採用貼文發布日(7/13)推測，非官方明確公告的活動起始日，請人工確認實際開幕日。貼文附圖為商品/場景實拍陳列照，非含名稱/日期文字的正式KV，故KV欄留空。</t>
+        </is>
+      </c>
+      <c r="O124" s="0" t="inlineStr">
+        <is>
+          <t>角落小夥伴</t>
+        </is>
+      </c>
+      <c r="P124" s="0" t="inlineStr">
+        <is>
+          <t>SAN-X</t>
+        </is>
+      </c>
+      <c r="Q124" s="17" t="n">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="0" t="inlineStr">
+        <is>
+          <t>物販/Goods</t>
+        </is>
+      </c>
+      <c r="C125" s="0" t="inlineStr">
+        <is>
+          <t>快閃店/Pop-up Store</t>
+        </is>
+      </c>
+      <c r="D125" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E125" s="0" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F125" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="G125" s="19" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H125" s="0" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="I125" s="0" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER POP UP SHOP</t>
+        </is>
+      </c>
+      <c r="J125" s="0" t="inlineStr">
+        <is>
+          <t>台北三創生活園區 6F INCUBASE Arena（台北市中正區市民大道三段2號6樓）</t>
+        </is>
+      </c>
+      <c r="K125" s="0" t="inlineStr">
+        <is>
+          <t>INCUBASE</t>
+        </is>
+      </c>
+      <c r="L125" s="0" t="inlineStr">
+        <is>
+          <t>AMNIBUS</t>
+        </is>
+      </c>
+      <c r="M125" s="0" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaNEtndDFyn/</t>
+        </is>
+      </c>
+      <c r="N125" s="0" t="inlineStr">
+        <is>
+          <t>資料來源：INCUBASE Arena Taipei官方IG(@incubase.arena.tp)6/30發布之官方巡迴公告(同步列出吉隆坡7/17-8/16、香港7/31-8/30、台北9/4-10/4三地)。原Slack訊息日期誤植為9/3，已依官方公告修正為9/4。連結為場館官方帳號直發貼文，非二手轉貼。</t>
+        </is>
+      </c>
+      <c r="O125" s="0" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="P125" s="0" t="inlineStr">
+        <is>
+          <t>AMNIBUS</t>
+        </is>
+      </c>
+      <c r="Q125" s="17" t="n">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="0" t="inlineStr">
+        <is>
+          <t>物販/Goods</t>
+        </is>
+      </c>
+      <c r="C126" s="0" t="inlineStr">
+        <is>
+          <t>快閃店/Pop-up Store</t>
+        </is>
+      </c>
+      <c r="D126" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E126" s="0" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F126" s="19" t="n">
+        <v>46219</v>
+      </c>
+      <c r="G126" s="19" t="n">
+        <v>46279</v>
+      </c>
+      <c r="H126" s="0" t="inlineStr">
+        <is>
+          <t>麵包超人</t>
+        </is>
+      </c>
+      <c r="I126" s="0" t="inlineStr">
+        <is>
+          <t>麵包超人夏日萌萌主題店</t>
+        </is>
+      </c>
+      <c r="J126" s="0" t="inlineStr">
+        <is>
+          <t>台中麗寶OUTLET MALL C區1樓中央廣場（台中市后里區福容路201號）</t>
+        </is>
+      </c>
+      <c r="M126" s="0" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Da2DfOEj_9k</t>
+        </is>
+      </c>
+      <c r="N126" s="0" t="inlineStr">
+        <is>
+          <t>資料來源：麵包超人台灣官方IG(@anpanman_tw)2026/07/16發布，確認日期(07/16-09/14)與地點，貼文含官方版權標示「© Takashi Yanase/ Froebel-kan, TMS, NTV」；連結為品牌官方帳號直發，非二手轉貼。地址由麗寶OUTLET官網(lihpaooutlet.com.tw)補查證。主辦/授權單位官方貼文未明確列出，暫留空待人工確認。</t>
+        </is>
+      </c>
+      <c r="O126" s="0" t="inlineStr">
+        <is>
+          <t>麵包超人</t>
+        </is>
+      </c>
+      <c r="Q126" s="17" t="n">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="0" t="inlineStr">
+        <is>
+          <t>物販/Goods</t>
+        </is>
+      </c>
+      <c r="C127" s="0" t="inlineStr">
+        <is>
+          <t>快閃店/Pop-up Store</t>
+        </is>
+      </c>
+      <c r="D127" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E127" s="0" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F127" s="19" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G127" s="19" t="n">
+        <v>46253</v>
+      </c>
+      <c r="H127" s="0" t="inlineStr">
+        <is>
+          <t>Tamagotchi塔麻可吉</t>
+        </is>
+      </c>
+      <c r="I127" s="0" t="inlineStr">
+        <is>
+          <t>Tamagotchi電子雞30週年紀念快閃店</t>
+        </is>
+      </c>
+      <c r="J127" s="0" t="inlineStr">
+        <is>
+          <t>新光三越台中中港店 10F（臺中市西屯區惠來里臺灣大道三段301號）</t>
+        </is>
+      </c>
+      <c r="K127" s="0" t="inlineStr">
+        <is>
+          <t>萬代國際(wangjungintl)</t>
+        </is>
+      </c>
+      <c r="L127" s="0" t="inlineStr">
+        <is>
+          <t>BANDAI</t>
+        </is>
+      </c>
+      <c r="M127" s="0" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DazKEteDD38</t>
+        </is>
+      </c>
+      <c r="N127" s="0" t="inlineStr">
+        <is>
+          <t>資料來源：萬代台灣代理官方IG(@wangjungintl)發布，明確列出日期(2026/7/27-8/19)、會場、地址，與原Slack訊息一致；連結為品牌官方帳號直發。此為台中場；另查得台北誠品生活南西場(07/16-07/31)為同系列巡迴的不同站點，非本筆，未另建列。</t>
+        </is>
+      </c>
+      <c r="O127" s="0" t="inlineStr">
+        <is>
+          <t>Tamagotchi塔麻可吉</t>
+        </is>
+      </c>
+      <c r="P127" s="0" t="inlineStr">
+        <is>
+          <t>BANDAI</t>
+        </is>
+      </c>
+      <c r="Q127" s="17" t="n">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/photo?fbid=1557479489724975&amp;set=pb.100063888157498.-2207520000</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>物販/Goods</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>快閃店/Pop-up Store</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F128" s="19" t="n">
+        <v>46219</v>
+      </c>
+      <c r="G128" s="19" t="n">
+        <v>46279</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sirotan</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Sirotan期間限定快閃店</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>台中麗寶OUTLET MALL C區1樓中央廣場（台中市后里區福容路201號）</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Sirotan台灣官方粉絲團</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>CREATIVE YOKO</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/photo?fbid=1557479489724975&amp;set=pb.100063888157498.-2207520000</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>資料與KV來源：Sirotan台灣官方Facebook粉絲團(8,903追蹤，簡介為「Sirotan台灣官方粉絲團」)，貼文日期2026/07/14，KV圖片經肉眼確認含「07.16-09.14」日期、「台中麗寶OUTLET MALL C區1樓 中央廣場」地點、Sirotan名稱與「Sirotan © CREATIVE YOKO」版權標示，與原Slack訊息日期地點一致。地址由麗寶OUTLET官網(lihpaooutlet.com.tw)補查證。連結為官方粉專貼文直發，非二手轉貼。</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Sirotan</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>CREATIVE YOKO</t>
+        </is>
+      </c>
+      <c r="Q128" s="17" t="n">
         <v>46204</v>
       </c>
     </row>
